--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -12365,7 +12365,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -22590,38 +22590,30 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H355" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I355" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H355" s="5" t="n">
+        <v>8150000</v>
+      </c>
+      <c r="I355" s="5" t="n">
+        <v>22576</v>
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K355" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L355" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K355" s="5" t="n">
+        <v>8150000</v>
+      </c>
+      <c r="L355" s="5" t="n">
+        <v>22576</v>
       </c>
       <c r="M355" s="3" t="inlineStr">
         <is>
@@ -22630,7 +22622,7 @@
       </c>
       <c r="N355" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23183,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23201,7 +23193,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -24888,7 +24880,7 @@
           <t>H | 399呎 (2房)
 $806万
 $20,189/呎
-(26年-08月-18日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -25142,7 +25134,7 @@
           <t>H | 399呎 (2房)
 $794万
 $19,901/呎
-(26年-08月-17日)</t>
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -26280,12 +26272,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 361呎 (2房)
-招标单位
--
-(在售)</t>
+$815万
+$22,576/呎
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -10505,7 +10505,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -24626,7 +24626,7 @@
           <t>H | 399呎 (2房)
 $819万
 $20,515/呎
-(26年-08月-21日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -25896,7 +25896,7 @@
           <t>H | 399呎 (2房)
 $772万
 $19,349/呎
-(26年-08月-16日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -13295,7 +13295,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -25007,7 +25007,7 @@
           <t>H | 399呎 (2房)
 $843万
 $21,130/呎
-(26年-08月-17日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -25515,7 +25515,7 @@
           <t>H | 399呎 (2房)
 $783万
 $19,614/呎
-(26年-08月-15日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -15155,7 +15155,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -25261,7 +25261,7 @@
           <t>H | 399呎 (2房)
 $790万
 $19,796/呎
-(26年-08月-29日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -9575,7 +9575,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23069,7 +23069,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -24499,7 +24499,7 @@
           <t>H | 399呎 (2房)
 $826万
 $20,695/呎
-(26年-08月-30日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -26221,7 +26221,7 @@
           <t>A | 605呎 (3房)
 $1634万
 $27,000/呎
-(26年-08月-27日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -26277,7 +26277,7 @@
           <t>H | 361呎 (2房)
 $815万
 $22,576/呎
-(26年-09月-04日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -116,13 +116,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -255,10 +255,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1626,38 +1626,30 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>18168600</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>28300</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K17" s="5" t="n">
+        <v>18168600</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>28300</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1666,7 +1658,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23183,7 +23175,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23193,7 +23185,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>354</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23298,12 +23290,12 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
+$1817万
+$28,300/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $861万
@@ -23311,7 +23303,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $847万
@@ -23319,7 +23311,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $841万
@@ -23327,7 +23319,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $841万
@@ -23335,7 +23327,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $860万
@@ -23343,7 +23335,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $830万
@@ -23351,7 +23343,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $824万
@@ -23359,7 +23351,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $756万
@@ -23367,7 +23359,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $764万
@@ -23375,7 +23367,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $780万
@@ -23383,7 +23375,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="M5" s="21" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $740万
@@ -23391,7 +23383,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="N5" s="21" t="inlineStr">
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $726万
@@ -23399,7 +23391,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="O5" s="21" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $721万
@@ -23407,7 +23399,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="P5" s="20" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 招标单位
@@ -23422,7 +23414,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1400万
@@ -23430,7 +23422,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $857万
@@ -23438,7 +23430,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $841万
@@ -23446,7 +23438,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $835万
@@ -23454,7 +23446,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $853万
@@ -23462,7 +23454,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $835万
@@ -23470,7 +23462,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $820万
@@ -23478,7 +23470,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $814万
@@ -23486,7 +23478,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $745万
@@ -23494,7 +23486,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $747万
@@ -23502,7 +23494,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $770万
@@ -23510,7 +23502,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="M6" s="21" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $729万
@@ -23518,7 +23510,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $720万
@@ -23526,7 +23518,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $714万
@@ -23534,7 +23526,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="P6" s="21" t="inlineStr">
+      <c r="P6" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $927万
@@ -23549,7 +23541,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1387万
@@ -23557,7 +23549,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $852万
@@ -23565,7 +23557,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $853万
@@ -23573,7 +23565,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $849万
@@ -23581,7 +23573,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $829万
@@ -23589,7 +23581,7 @@
 (26年-05月-29日)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $827万
@@ -23597,7 +23589,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $812万
@@ -23605,7 +23597,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $803万
@@ -23613,7 +23605,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $735万
@@ -23621,7 +23613,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $776万
@@ -23629,7 +23621,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $747万
@@ -23637,7 +23629,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="M7" s="21" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $722万
@@ -23645,7 +23637,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $713万
@@ -23653,7 +23645,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="O7" s="21" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $709万
@@ -23661,7 +23653,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="P7" s="21" t="inlineStr">
+      <c r="P7" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $919万
@@ -23676,7 +23668,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1377万
@@ -23684,7 +23676,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $848万
@@ -23692,7 +23684,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $827万
@@ -23700,7 +23692,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $827万
@@ -23708,7 +23700,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $825万
@@ -23716,7 +23708,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $818万
@@ -23724,7 +23716,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $802万
@@ -23732,7 +23724,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $795万
@@ -23740,7 +23732,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $725万
@@ -23748,7 +23740,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $726万
@@ -23756,7 +23748,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="L8" s="21" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $740万
@@ -23764,7 +23756,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="M8" s="21" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $731万
@@ -23772,7 +23764,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="N8" s="21" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $722万
@@ -23780,7 +23772,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="O8" s="21" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $720万
@@ -23788,7 +23780,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="P8" s="21" t="inlineStr">
+      <c r="P8" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $912万
@@ -23803,7 +23795,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1367万
@@ -23811,7 +23803,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $844万
@@ -23819,7 +23811,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $821万
@@ -23827,7 +23819,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $823万
@@ -23835,7 +23827,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $819万
@@ -23843,7 +23835,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $856万
@@ -23851,7 +23843,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $796万
@@ -23859,7 +23851,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $788万
@@ -23867,7 +23859,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $733万
@@ -23875,7 +23867,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $715万
@@ -23883,7 +23875,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $732万
@@ -23891,7 +23883,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="M9" s="21" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $725万
@@ -23899,7 +23891,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $698万
@@ -23907,7 +23899,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="O9" s="21" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $735万
@@ -23915,7 +23907,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="P9" s="21" t="inlineStr">
+      <c r="P9" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $905万
@@ -23930,7 +23922,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1359万
@@ -23938,7 +23930,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $838万
@@ -23946,7 +23938,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $860万
@@ -23954,7 +23946,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $864万
@@ -23962,7 +23954,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $857万
@@ -23970,7 +23962,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $852万
@@ -23978,7 +23970,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $789万
@@ -23986,7 +23978,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $799万
@@ -23994,7 +23986,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $713万
@@ -24002,7 +23994,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $709万
@@ -24010,7 +24002,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $766万
@@ -24018,7 +24010,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="M10" s="21" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $722万
@@ -24026,7 +24018,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="N10" s="21" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $694万
@@ -24034,7 +24026,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="O10" s="21" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $688万
@@ -24042,7 +24034,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="P10" s="21" t="inlineStr">
+      <c r="P10" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $898万
@@ -24057,7 +24049,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1350万
@@ -24065,7 +24057,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $849万
@@ -24073,7 +24065,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $811万
@@ -24081,7 +24073,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $814万
@@ -24089,7 +24081,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $809万
@@ -24097,7 +24089,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $845万
@@ -24105,7 +24097,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $779万
@@ -24113,7 +24105,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $775万
@@ -24121,7 +24113,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="J11" s="21" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $709万
@@ -24129,7 +24121,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $747万
@@ -24137,7 +24129,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="L11" s="21" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $762万
@@ -24145,7 +24137,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="M11" s="21" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $742万
@@ -24153,7 +24145,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="N11" s="21" t="inlineStr">
+      <c r="N11" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $705万
@@ -24161,7 +24153,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="O11" s="21" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $686万
@@ -24169,7 +24161,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="P11" s="21" t="inlineStr">
+      <c r="P11" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $891万
@@ -24184,7 +24176,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1340万
@@ -24192,7 +24184,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $825万
@@ -24200,7 +24192,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $806万
@@ -24208,7 +24200,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $852万
@@ -24216,7 +24208,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $802万
@@ -24224,7 +24216,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $795万
@@ -24232,7 +24224,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $769万
@@ -24240,7 +24232,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $811万
@@ -24248,7 +24240,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $703万
@@ -24256,7 +24248,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $704万
@@ -24264,7 +24256,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $718万
@@ -24272,7 +24264,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="M12" s="21" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $738万
@@ -24280,7 +24272,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="N12" s="21" t="inlineStr">
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $686万
@@ -24288,7 +24280,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="O12" s="21" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $684万
@@ -24296,7 +24288,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="P12" s="21" t="inlineStr">
+      <c r="P12" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $888万
@@ -24311,7 +24303,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1345万
@@ -24319,7 +24311,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $818万
@@ -24327,7 +24319,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $799万
@@ -24335,7 +24327,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $845万
@@ -24343,7 +24335,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $796万
@@ -24351,7 +24343,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $786万
@@ -24359,7 +24351,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $741万
@@ -24367,7 +24359,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $805万
@@ -24375,7 +24367,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $735万
@@ -24383,7 +24375,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="K13" s="21" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $695万
@@ -24391,7 +24383,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $715万
@@ -24399,7 +24391,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="M13" s="21" t="inlineStr">
+      <c r="M13" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $734万
@@ -24407,7 +24399,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="N13" s="21" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $699万
@@ -24415,7 +24407,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="O13" s="21" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $719万
@@ -24423,7 +24415,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="P13" s="21" t="inlineStr">
+      <c r="P13" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $905万
@@ -24438,7 +24430,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1320万
@@ -24446,7 +24438,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $810万
@@ -24454,7 +24446,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $792万
@@ -24462,7 +24454,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $810万
@@ -24470,7 +24462,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $798万
@@ -24478,7 +24470,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $779万
@@ -24486,7 +24478,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $738万
@@ -24494,7 +24486,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $826万
@@ -24502,7 +24494,7 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $690万
@@ -24510,7 +24502,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $686万
@@ -24518,7 +24510,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $712万
@@ -24526,7 +24518,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="M14" s="21" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $729万
@@ -24534,7 +24526,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $681万
@@ -24542,7 +24534,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="O14" s="21" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $676万
@@ -24550,7 +24542,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="P14" s="21" t="inlineStr">
+      <c r="P14" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $882万
@@ -24565,7 +24557,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1301万
@@ -24573,7 +24565,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $802万
@@ -24581,7 +24573,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $786万
@@ -24589,7 +24581,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $803万
@@ -24597,7 +24589,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $774万
@@ -24605,7 +24597,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $772万
@@ -24613,7 +24605,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $736万
@@ -24621,7 +24613,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $819万
@@ -24629,7 +24621,7 @@
 (26年-09月-10日)</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $683万
@@ -24637,7 +24629,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="K15" s="21" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $677万
@@ -24645,7 +24637,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="L15" s="21" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $704万
@@ -24653,7 +24645,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="M15" s="21" t="inlineStr">
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $726万
@@ -24661,7 +24653,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="N15" s="21" t="inlineStr">
+      <c r="N15" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $675万
@@ -24669,7 +24661,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="O15" s="21" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $673万
@@ -24677,7 +24669,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="P15" s="21" t="inlineStr">
+      <c r="P15" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $879万
@@ -24692,7 +24684,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1251万
@@ -24700,7 +24692,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $796万
@@ -24708,7 +24700,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $799万
@@ -24716,7 +24708,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $778万
@@ -24724,7 +24716,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $763万
@@ -24732,7 +24724,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $766万
@@ -24740,7 +24732,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $732万
@@ -24748,7 +24740,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $811万
@@ -24756,7 +24748,7 @@
 (26年-09月-03日)</t>
         </is>
       </c>
-      <c r="J16" s="21" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $689万
@@ -24764,7 +24756,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="K16" s="21" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $712万
@@ -24772,7 +24764,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="L16" s="21" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $699万
@@ -24780,7 +24772,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="M16" s="21" t="inlineStr">
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $700万
@@ -24788,7 +24780,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="N16" s="21" t="inlineStr">
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $666万
@@ -24796,7 +24788,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="O16" s="21" t="inlineStr">
+      <c r="O16" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $668万
@@ -24804,7 +24796,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="P16" s="21" t="inlineStr">
+      <c r="P16" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $876万
@@ -24819,7 +24811,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1231万
@@ -24827,7 +24819,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $832万
@@ -24835,7 +24827,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $776万
@@ -24843,7 +24835,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $788万
@@ -24851,7 +24843,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $751万
@@ -24859,7 +24851,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $797万
@@ -24867,7 +24859,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $727万
@@ -24875,7 +24867,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $806万
@@ -24883,7 +24875,7 @@
 (26年-09月-04日)</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $686万
@@ -24891,7 +24883,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="K17" s="21" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $687万
@@ -24899,7 +24891,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="L17" s="21" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $693万
@@ -24907,7 +24899,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="M17" s="21" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $719万
@@ -24915,7 +24907,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="N17" s="21" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $661万
@@ -24923,7 +24915,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="O17" s="21" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $662万
@@ -24931,7 +24923,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="P17" s="21" t="inlineStr">
+      <c r="P17" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $921万
@@ -24946,7 +24938,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1215万
@@ -24954,7 +24946,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $824万
@@ -24962,7 +24954,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $771万
@@ -24970,7 +24962,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $808万
@@ -24978,7 +24970,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $738万
@@ -24986,7 +24978,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $745万
@@ -24994,7 +24986,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $764万
@@ -25002,7 +24994,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $843万
@@ -25010,7 +25002,7 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="J18" s="21" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $669万
@@ -25018,7 +25010,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K18" s="21" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $670万
@@ -25026,7 +25018,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="L18" s="21" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $689万
@@ -25034,7 +25026,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="M18" s="21" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $713万
@@ -25042,7 +25034,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="N18" s="21" t="inlineStr">
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $658万
@@ -25050,7 +25042,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="O18" s="21" t="inlineStr">
+      <c r="O18" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $660万
@@ -25058,7 +25050,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="P18" s="21" t="inlineStr">
+      <c r="P18" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $870万
@@ -25073,7 +25065,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1211万
@@ -25081,7 +25073,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $777万
@@ -25089,7 +25081,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $768万
@@ -25097,7 +25089,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $762万
@@ -25105,7 +25097,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $761万
@@ -25113,7 +25105,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $776万
@@ -25121,7 +25113,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $722万
@@ -25129,7 +25121,7 @@
 (26年-04月-25日)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $794万
@@ -25137,7 +25129,7 @@
 (26年-09月-07日)</t>
         </is>
       </c>
-      <c r="J19" s="21" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $667万
@@ -25145,7 +25137,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K19" s="21" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $704万
@@ -25153,7 +25145,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="L19" s="21" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $722万
@@ -25161,7 +25153,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="M19" s="21" t="inlineStr">
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $709万
@@ -25169,7 +25161,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="N19" s="21" t="inlineStr">
+      <c r="N19" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $656万
@@ -25177,7 +25169,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="O19" s="21" t="inlineStr">
+      <c r="O19" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $658万
@@ -25185,7 +25177,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="P19" s="21" t="inlineStr">
+      <c r="P19" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $867万
@@ -25200,7 +25192,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1207万
@@ -25208,7 +25200,7 @@
 (26年-04月-25日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $790万
@@ -25216,7 +25208,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $761万
@@ -25224,7 +25216,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $799万
@@ -25232,7 +25224,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $708万
@@ -25240,7 +25232,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $718万
@@ -25248,7 +25240,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $759万
@@ -25256,7 +25248,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $790万
@@ -25264,7 +25256,7 @@
 (26年-09月-18日)</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $664万
@@ -25272,7 +25264,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K20" s="21" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $665万
@@ -25280,7 +25272,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="L20" s="21" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $680万
@@ -25288,7 +25280,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="M20" s="21" t="inlineStr">
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $668万
@@ -25296,7 +25288,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="N20" s="21" t="inlineStr">
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $654万
@@ -25304,7 +25296,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="O20" s="21" t="inlineStr">
+      <c r="O20" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $655万
@@ -25312,7 +25304,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="P20" s="21" t="inlineStr">
+      <c r="P20" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $864万
@@ -25327,7 +25319,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1229万
@@ -25335,7 +25327,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $786万
@@ -25343,7 +25335,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $757万
@@ -25351,7 +25343,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $752万
@@ -25359,7 +25351,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $706万
@@ -25367,7 +25359,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $716万
@@ -25375,7 +25367,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $717万
@@ -25383,7 +25375,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $786万
@@ -25391,7 +25383,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $662万
@@ -25399,7 +25391,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K21" s="21" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $676万
@@ -25407,7 +25399,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="L21" s="21" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $676万
@@ -25415,7 +25407,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="M21" s="21" t="inlineStr">
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $666万
@@ -25423,7 +25415,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="N21" s="21" t="inlineStr">
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $653万
@@ -25431,7 +25423,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="O21" s="21" t="inlineStr">
+      <c r="O21" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $654万
@@ -25439,7 +25431,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="P21" s="21" t="inlineStr">
+      <c r="P21" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $861万
@@ -25454,7 +25446,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1198万
@@ -25462,7 +25454,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $765万
@@ -25470,7 +25462,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $796万
@@ -25478,7 +25470,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $749万
@@ -25486,7 +25478,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $703万
@@ -25494,7 +25486,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $713万
@@ -25502,7 +25494,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $730万
@@ -25510,7 +25502,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $783万
@@ -25518,7 +25510,7 @@
 (26年-09月-14日)</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $660万
@@ -25526,7 +25518,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K22" s="21" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $656万
@@ -25534,7 +25526,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="L22" s="21" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $685万
@@ -25542,7 +25534,7 @@
 (26年-04月-25日)</t>
         </is>
       </c>
-      <c r="M22" s="21" t="inlineStr">
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $663万
@@ -25550,7 +25542,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="N22" s="21" t="inlineStr">
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $651万
@@ -25558,7 +25550,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="O22" s="21" t="inlineStr">
+      <c r="O22" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $653万
@@ -25566,7 +25558,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="P22" s="21" t="inlineStr">
+      <c r="P22" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $905万
@@ -25581,7 +25573,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1194万
@@ -25589,7 +25581,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $802万
@@ -25597,7 +25589,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $793万
@@ -25605,7 +25597,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $746万
@@ -25613,7 +25605,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $701万
@@ -25621,7 +25613,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $750万
@@ -25629,7 +25621,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $711万
@@ -25637,7 +25629,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $779万
@@ -25645,7 +25637,7 @@
 (26年-09月-01日)</t>
         </is>
       </c>
-      <c r="J23" s="21" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $693万
@@ -25653,7 +25645,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K23" s="21" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $690万
@@ -25661,7 +25653,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="L23" s="21" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $664万
@@ -25669,7 +25661,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="M23" s="21" t="inlineStr">
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $661万
@@ -25677,7 +25669,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="N23" s="21" t="inlineStr">
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $650万
@@ -25685,7 +25677,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="O23" s="21" t="inlineStr">
+      <c r="O23" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $652万
@@ -25693,7 +25685,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="P23" s="21" t="inlineStr">
+      <c r="P23" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $854万
@@ -25708,7 +25700,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1218万
@@ -25716,7 +25708,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $758万
@@ -25724,7 +25716,7 @@
 (26年-05月-29日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $789万
@@ -25732,7 +25724,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $758万
@@ -25740,7 +25732,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $699万
@@ -25748,7 +25740,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $709万
@@ -25756,7 +25748,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $710万
@@ -25764,7 +25756,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $776万
@@ -25772,7 +25764,7 @@
 (26年-09月-03日)</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $670万
@@ -25780,7 +25772,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K24" s="21" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $667万
@@ -25788,7 +25780,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="L24" s="21" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $660万
@@ -25796,7 +25788,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="M24" s="21" t="inlineStr">
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $659万
@@ -25804,7 +25796,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="N24" s="21" t="inlineStr">
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $646万
@@ -25812,7 +25804,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="O24" s="21" t="inlineStr">
+      <c r="O24" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $651万
@@ -25820,7 +25812,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="P24" s="21" t="inlineStr">
+      <c r="P24" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $899万
@@ -25835,7 +25827,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1187万
@@ -25843,7 +25835,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $755万
@@ -25851,7 +25843,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $746万
@@ -25859,7 +25851,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $756万
@@ -25867,7 +25859,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $698万
@@ -25875,7 +25867,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $708万
@@ -25883,7 +25875,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $709万
@@ -25891,7 +25883,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $772万
@@ -25899,7 +25891,7 @@
 (26年-09月-08日)</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $688万
@@ -25907,7 +25899,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K25" s="21" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $649万
@@ -25915,7 +25907,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="L25" s="21" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $656万
@@ -25923,7 +25915,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="M25" s="21" t="inlineStr">
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $656万
@@ -25931,7 +25923,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="N25" s="21" t="inlineStr">
+      <c r="N25" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $645万
@@ -25939,7 +25931,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="O25" s="21" t="inlineStr">
+      <c r="O25" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $647万
@@ -25947,7 +25939,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="P25" s="21" t="inlineStr">
+      <c r="P25" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $848万
@@ -25962,7 +25954,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1185万
@@ -25970,7 +25962,7 @@
 (26年-04月-25日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $752万
@@ -25978,7 +25970,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $741万
@@ -25986,7 +25978,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $735万
@@ -25994,7 +25986,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $697万
@@ -26002,7 +25994,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $707万
@@ -26010,7 +26002,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $746万
@@ -26018,7 +26010,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $698万
@@ -26026,7 +26018,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $650万
@@ -26034,7 +26026,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="K26" s="21" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $661万
@@ -26042,7 +26034,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="L26" s="21" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $654万
@@ -26050,7 +26042,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="M26" s="21" t="inlineStr">
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $654万
@@ -26058,7 +26050,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="N26" s="21" t="inlineStr">
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $643万
@@ -26066,7 +26058,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="O26" s="21" t="inlineStr">
+      <c r="O26" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $645万
@@ -26074,7 +26066,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="P26" s="21" t="inlineStr">
+      <c r="P26" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $864万
@@ -26089,7 +26081,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 $1183万
@@ -26097,7 +26089,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 390呎 (2房)
 $751万
@@ -26105,7 +26097,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 388呎 (2房)
 $753万
@@ -26113,7 +26105,7 @@
 (26年-04月-25日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $730万
@@ -26121,7 +26113,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 393呎 (2房)
 $696万
@@ -26129,7 +26121,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 399呎 (2房)
 $706万
@@ -26137,7 +26129,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 $703万
@@ -26145,7 +26137,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
 $693万
@@ -26153,7 +26145,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
 $678万
@@ -26161,7 +26153,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K27" s="21" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
 $641万
@@ -26169,7 +26161,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="L27" s="21" t="inlineStr">
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
 $648万
@@ -26177,7 +26169,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="M27" s="21" t="inlineStr">
+      <c r="M27" s="20" t="inlineStr">
         <is>
           <t>M | 339呎 (2房)
 $648万
@@ -26185,7 +26177,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="N27" s="21" t="inlineStr">
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>N | 339呎 (2房)
 $673万
@@ -26193,7 +26185,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="O27" s="21" t="inlineStr">
+      <c r="O27" s="20" t="inlineStr">
         <is>
           <t>P | 343呎 (2房)
 $657万
@@ -26201,7 +26193,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="P27" s="21" t="inlineStr">
+      <c r="P27" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $842万
@@ -26216,7 +26208,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 605呎 (3房)
 $1634万
@@ -26224,7 +26216,7 @@
 (26年-09月-23日)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 352呎 (2房)
 招标单位
@@ -26232,7 +26224,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
 $847万
@@ -26240,7 +26232,7 @@
 (26年-09月-01日)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 352呎 (2房)
 招标单位
@@ -26248,7 +26240,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 355呎 (2房)
 招标单位
@@ -26256,7 +26248,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 362呎 (2房)
 招标单位
@@ -26264,7 +26256,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 360呎 (2房)
 招标单位
@@ -26272,7 +26264,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 361呎 (2房)
 $815万
@@ -26280,7 +26272,7 @@
 (26年-09月-23日)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 301呎 (2房)
 $714万
@@ -26288,7 +26280,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="K28" s="21" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
         <is>
           <t>K | 301呎 (2房)
 $715万
@@ -26296,7 +26288,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="L28" s="21" t="inlineStr">
+      <c r="L28" s="20" t="inlineStr">
         <is>
           <t>L | 301呎 (2房)
 $705万
@@ -26304,7 +26296,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="M28" s="21" t="inlineStr">
+      <c r="M28" s="20" t="inlineStr">
         <is>
           <t>M | 301呎 (2房)
 $690万
@@ -26312,7 +26304,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="N28" s="21" t="inlineStr">
+      <c r="N28" s="20" t="inlineStr">
         <is>
           <t>N | 301呎 (2房)
 $687万
@@ -26320,7 +26312,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="O28" s="21" t="inlineStr">
+      <c r="O28" s="20" t="inlineStr">
         <is>
           <t>P | 306呎 (2房)
 $701万
@@ -26328,7 +26320,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="P28" s="21" t="inlineStr">
+      <c r="P28" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $912万

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -18743,14 +18743,14 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
-        <v>6669900</v>
+        <v>6526500</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>19675</v>
+        <v>19252</v>
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
@@ -18758,10 +18758,10 @@
         </is>
       </c>
       <c r="K293" s="5" t="n">
-        <v>6669900</v>
+        <v>6526500</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>19675</v>
+        <v>19252</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
@@ -25775,9 +25775,9 @@
       <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
-$667万
-$19,675/呎
-(26年-05月-20日)</t>
+$653万
+$19,252/呎
+(26年-04月-25日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -13287,14 +13287,14 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
-        <v>8430700</v>
+        <v>8167200</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>21130</v>
+        <v>20469</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -13302,10 +13302,10 @@
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>8430700</v>
+        <v>8167200</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>21130</v>
+        <v>20469</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -24997,9 +24997,9 @@
       <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$843万
-$21,130/呎
-(26年-09月-11日)</t>
+$817万
+$20,469/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -23292,7 +23292,7 @@
           <t>A | 642呎 (3房)
 $1817万
 $28,300/呎
-(26年-10月-02日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -121,8 +121,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -258,7 +257,7 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -750,7 +749,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -760,12 +759,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -775,12 +774,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -790,7 +789,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22644,7 +22643,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -22654,12 +22653,12 @@
       </c>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J356" s="3" t="inlineStr">
@@ -22669,12 +22668,12 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M356" s="3" t="inlineStr">
@@ -22684,7 +22683,7 @@
       </c>
       <c r="N356" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22713,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -22724,12 +22723,12 @@
       </c>
       <c r="H357" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J357" s="3" t="inlineStr">
@@ -22739,12 +22738,12 @@
       </c>
       <c r="K357" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M357" s="3" t="inlineStr">
@@ -22754,7 +22753,7 @@
       </c>
       <c r="N357" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22784,7 +22783,7 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -22794,12 +22793,12 @@
       </c>
       <c r="H358" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J358" s="3" t="inlineStr">
@@ -22809,12 +22808,12 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M358" s="3" t="inlineStr">
@@ -22824,7 +22823,7 @@
       </c>
       <c r="N358" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22853,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -22864,12 +22863,12 @@
       </c>
       <c r="H359" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I359" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J359" s="3" t="inlineStr">
@@ -22879,12 +22878,12 @@
       </c>
       <c r="K359" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L359" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M359" s="3" t="inlineStr">
@@ -22894,7 +22893,7 @@
       </c>
       <c r="N359" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22986,7 +22985,7 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -22996,12 +22995,12 @@
       </c>
       <c r="H361" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J361" s="3" t="inlineStr">
@@ -23011,12 +23010,12 @@
       </c>
       <c r="K361" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M361" s="3" t="inlineStr">
@@ -23026,7 +23025,7 @@
       </c>
       <c r="N361" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23175,27 +23174,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -23402,9 +23401,9 @@
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -26219,9 +26218,9 @@
       <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 352呎 (2房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -26235,33 +26234,33 @@
       <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 352呎 (2房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 355呎 (2房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 362呎 (2房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 360呎 (2房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
